--- a/liste prix ventes articles part2.xlsx
+++ b/liste prix ventes articles part2.xlsx
@@ -15202,7 +15202,7 @@
         </is>
       </c>
       <c r="C986" t="n">
-        <v>600</v>
+        <v>650</v>
       </c>
     </row>
     <row r="987">
@@ -23392,7 +23392,7 @@
         </is>
       </c>
       <c r="C1532" t="n">
-        <v>1050</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="1533">
@@ -23467,7 +23467,7 @@
         </is>
       </c>
       <c r="C1537" t="n">
-        <v>1050</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="1538">
@@ -29431,7 +29431,7 @@
         </is>
       </c>
       <c r="C1935" t="n">
-        <v>1750</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="1936">
@@ -29517,7 +29517,7 @@
       </c>
       <c r="B1941" t="inlineStr">
         <is>
-          <t>GEL DE DOUCHE DOP LAIT VEGETAL 290ML</t>
+          <t>GEL DE DOUCHE DOP ASS  290ML</t>
         </is>
       </c>
       <c r="C1941" t="n">
@@ -29821,7 +29821,7 @@
         </is>
       </c>
       <c r="C1961" t="n">
-        <v>2800</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1962">
